--- a/Student_Marksheet.xlsx
+++ b/Student_Marksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chjit\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56326EF3-547E-44A4-B18C-498C70ACD0E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AABB5DB-E122-4130-8DEA-2E7A8BC15245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{71D4EC96-C3F1-42DB-B1DA-DF409C3E0C78}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Student Name</t>
   </si>
@@ -73,6 +73,15 @@
   </si>
   <si>
     <t>harinika</t>
+  </si>
+  <si>
+    <t>Trimmed Name</t>
+  </si>
+  <si>
+    <t>Clean Student NameTrimmed Name</t>
+  </si>
+  <si>
+    <t>Error Handling</t>
   </si>
 </sst>
 </file>
@@ -81,7 +90,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;?_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;?_ ;_ @_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -113,7 +122,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -126,8 +135,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -150,14 +165,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -166,7 +189,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -482,190 +507,298 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DEF7BCB-A0D6-48C7-A3B1-6ADDE776AB80}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="7" max="7" width="17.77734375" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="9.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="G1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="6"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>58</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>63</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>99</v>
       </c>
-      <c r="E2" s="4">
-        <f>SUM(B2:D2)</f>
+      <c r="E2" s="3">
+        <f t="shared" ref="E2:E8" si="0">SUM(B2:D2)</f>
         <v>220</v>
       </c>
-      <c r="F2" s="6">
-        <f>AVERAGE(B2:D2)</f>
+      <c r="F2" s="5">
+        <f t="shared" ref="F2:F8" si="1">AVERAGE(B2:D2)</f>
         <v>73.333333333333329</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="G2" t="str">
+        <f t="shared" ref="G2:G10" si="2">PROPER(A2)</f>
+        <v>Poojitha</v>
+      </c>
+      <c r="H2" t="str">
+        <f>TRIM(A2)</f>
+        <v>poojitha</v>
+      </c>
+      <c r="I2" t="str">
+        <f>IFERROR(10/0,"No Error")</f>
+        <v>No Error</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>56</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>84</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>57</v>
       </c>
-      <c r="E3" s="4">
-        <f t="shared" ref="E3:E8" si="0">SUM(B3:D3)</f>
+      <c r="E3" s="3">
+        <f t="shared" si="0"/>
         <v>197</v>
       </c>
-      <c r="F3" s="6">
-        <f t="shared" ref="F3:F9" si="1">AVERAGE(B3:D3)</f>
+      <c r="F3" s="5">
+        <f t="shared" si="1"/>
         <v>65.666666666666671</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="G3" t="str">
+        <f t="shared" si="2"/>
+        <v>Akanksha</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H8" si="3">TRIM(A3)</f>
+        <v>akanksha</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I8" si="4">IFERROR(10/0,"No Error")</f>
+        <v>No Error</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>54</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>96</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>67</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <f t="shared" si="0"/>
         <v>217</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <f t="shared" si="1"/>
         <v>72.333333333333329</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="G4" t="str">
+        <f t="shared" si="2"/>
+        <v>Gayathri</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="3"/>
+        <v>gayathri</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="4"/>
+        <v>No Error</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>52</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>54</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>82</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <f t="shared" si="0"/>
         <v>188</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <f t="shared" si="1"/>
         <v>62.666666666666664</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="G5" t="str">
+        <f t="shared" si="2"/>
+        <v>Varshitha</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="3"/>
+        <v>varshitha</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="4"/>
+        <v>No Error</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>50</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>63</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>50</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <f t="shared" si="1"/>
         <v>54.333333333333336</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="G6" t="str">
+        <f t="shared" si="2"/>
+        <v>Lahari</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="3"/>
+        <v>lahari</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="4"/>
+        <v>No Error</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>48</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>82</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>60</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <f t="shared" si="1"/>
         <v>63.333333333333336</v>
       </c>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+      <c r="G7" t="str">
+        <f t="shared" si="2"/>
+        <v>Lalanika</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="3"/>
+        <v>lalanika</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="4"/>
+        <v>No Error</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>46</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>44</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>40</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <f t="shared" si="1"/>
         <v>43.333333333333336</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="G8" t="str">
+        <f t="shared" si="2"/>
+        <v>Harinika</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="3"/>
+        <v>harinika</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="4"/>
+        <v>No Error</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G10" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
